--- a/data/fixture-tabellbilaga.xlsx
+++ b/data/fixture-tabellbilaga.xlsx
@@ -14,13 +14,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="243">
   <si>
     <t xml:space="preserve">Bas: Samtliga 18+ år
 Använder du internet?</t>
   </si>
   <si>
-    <t>Cellinnehåll: Kolumn% Chi2</t>
+    <t xml:space="preserve">Cellinnehåll:
+ Kolumn%
+ Chi2 nivå(W):95%
+</t>
   </si>
   <si>
     <t/>
@@ -1133,14 +1136,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1155,66 +1221,66 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -1620,8 +1686,71 @@
         <v>0.4828</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="V10" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1636,66 +1765,66 @@
         <v>3</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -1763,409 +1892,341 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13">
-        <v>2934</v>
+        <v>2843</v>
       </c>
       <c r="C13">
-        <v>1438</v>
+        <v>1415</v>
       </c>
       <c r="D13">
-        <v>1496</v>
+        <v>1413</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="G13">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="H13">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="I13">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J13">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="K13">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="L13">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="M13">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="N13">
-        <v>964</v>
+        <v>1017</v>
       </c>
       <c r="O13">
-        <v>1373</v>
+        <v>1346</v>
       </c>
       <c r="P13">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="Q13">
-        <v>611</v>
+        <v>629</v>
       </c>
       <c r="R13">
-        <v>803</v>
+        <v>765</v>
       </c>
       <c r="S13">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="T13">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="U13">
-        <v>1189</v>
+        <v>1256</v>
       </c>
       <c r="V13">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B14">
-        <v>2843</v>
+        <v>0.6609</v>
       </c>
       <c r="C14">
-        <v>1415</v>
+        <v>0.6416</v>
       </c>
       <c r="D14">
-        <v>1413</v>
+        <v>0.6341</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>276</v>
+        <v>0.5506</v>
       </c>
       <c r="G14">
-        <v>396</v>
-      </c>
-      <c r="H14">
-        <v>436</v>
+        <v>0.5491</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
       </c>
       <c r="I14">
-        <v>398</v>
+        <v>0.7492</v>
       </c>
       <c r="J14">
-        <v>419</v>
+        <v>0.793</v>
       </c>
       <c r="K14">
-        <v>393</v>
+        <v>0.7486</v>
       </c>
       <c r="L14">
-        <v>200</v>
+        <v>0.4961</v>
       </c>
       <c r="M14">
-        <v>182</v>
+        <v>0.5964</v>
       </c>
       <c r="N14">
-        <v>1017</v>
+        <v>0.6029</v>
       </c>
       <c r="O14">
-        <v>1346</v>
+        <v>0.783</v>
       </c>
       <c r="P14">
-        <v>725</v>
+        <v>0.7862</v>
       </c>
       <c r="Q14">
-        <v>629</v>
-      </c>
-      <c r="R14">
-        <v>765</v>
+        <v>0.6426</v>
+      </c>
+      <c r="R14" t="s">
+        <v>42</v>
       </c>
       <c r="S14">
-        <v>371</v>
+        <v>0.4911</v>
       </c>
       <c r="T14">
-        <v>1103</v>
+        <v>0.731</v>
       </c>
       <c r="U14">
-        <v>1256</v>
+        <v>0.806</v>
       </c>
       <c r="V14">
-        <v>226</v>
+        <v>0.5393</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B15">
-        <v>0.6609</v>
+        <v>0.5282</v>
       </c>
       <c r="C15">
-        <v>0.6416</v>
+        <v>0.3599</v>
       </c>
       <c r="D15">
-        <v>0.6341</v>
+        <v>0.5302</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0.5506</v>
+        <v>0.6565</v>
       </c>
       <c r="G15">
-        <v>0.5491</v>
-      </c>
-      <c r="H15" t="s">
-        <v>41</v>
+        <v>0.5444</v>
+      </c>
+      <c r="H15">
+        <v>0.5793</v>
       </c>
       <c r="I15">
-        <v>0.7492</v>
-      </c>
-      <c r="J15">
-        <v>0.793</v>
-      </c>
-      <c r="K15">
-        <v>0.7486</v>
+        <v>0.5396</v>
+      </c>
+      <c r="J15" t="s">
+        <v>44</v>
+      </c>
+      <c r="K15" t="s">
+        <v>45</v>
       </c>
       <c r="L15">
-        <v>0.4961</v>
+        <v>0.4642</v>
       </c>
       <c r="M15">
-        <v>0.5964</v>
+        <v>0.5115</v>
       </c>
       <c r="N15">
-        <v>0.6029</v>
+        <v>0.433</v>
       </c>
       <c r="O15">
-        <v>0.783</v>
+        <v>0.4386</v>
       </c>
       <c r="P15">
-        <v>0.7862</v>
+        <v>0.5113</v>
       </c>
       <c r="Q15">
-        <v>0.6426</v>
-      </c>
-      <c r="R15" t="s">
-        <v>42</v>
-      </c>
-      <c r="S15">
-        <v>0.4911</v>
-      </c>
-      <c r="T15">
-        <v>0.731</v>
+        <v>0.3884</v>
+      </c>
+      <c r="R15">
+        <v>0.6163</v>
+      </c>
+      <c r="S15" t="s">
+        <v>46</v>
+      </c>
+      <c r="T15" t="s">
+        <v>47</v>
       </c>
       <c r="U15">
-        <v>0.806</v>
+        <v>0.5969</v>
       </c>
       <c r="V15">
-        <v>0.5393</v>
+        <v>0.5089</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B16">
-        <v>0.5282</v>
+        <v>0.4275</v>
       </c>
       <c r="C16">
-        <v>0.3599</v>
+        <v>0.4972</v>
       </c>
       <c r="D16">
-        <v>0.5302</v>
+        <v>0.3628</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>0.6565</v>
+        <v>0.5343</v>
       </c>
       <c r="G16">
-        <v>0.5444</v>
+        <v>0.2628</v>
       </c>
       <c r="H16">
-        <v>0.5793</v>
+        <v>0.5541</v>
       </c>
       <c r="I16">
-        <v>0.5396</v>
+        <v>0.3383</v>
       </c>
       <c r="J16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K16" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L16">
-        <v>0.4642</v>
+        <v>0.5027</v>
       </c>
       <c r="M16">
-        <v>0.5115</v>
+        <v>0.5842</v>
       </c>
       <c r="N16">
-        <v>0.433</v>
+        <v>0.2993</v>
       </c>
       <c r="O16">
-        <v>0.4386</v>
-      </c>
-      <c r="P16">
-        <v>0.5113</v>
+        <v>0.5482</v>
+      </c>
+      <c r="P16" t="s">
+        <v>51</v>
       </c>
       <c r="Q16">
-        <v>0.3884</v>
+        <v>0.3394</v>
       </c>
       <c r="R16">
-        <v>0.6163</v>
-      </c>
-      <c r="S16" t="s">
-        <v>46</v>
-      </c>
-      <c r="T16" t="s">
-        <v>47</v>
+        <v>0.5828</v>
+      </c>
+      <c r="S16">
+        <v>0.4412</v>
+      </c>
+      <c r="T16">
+        <v>0.5823</v>
       </c>
       <c r="U16">
-        <v>0.5969</v>
+        <v>0.4137</v>
       </c>
       <c r="V16">
-        <v>0.5089</v>
+        <v>0.3706</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B17">
-        <v>0.4275</v>
+        <v>0.3219</v>
       </c>
       <c r="C17">
-        <v>0.4972</v>
+        <v>0.2074</v>
       </c>
       <c r="D17">
-        <v>0.3628</v>
+        <v>0.3037</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0.5343</v>
+        <v>0.271</v>
       </c>
       <c r="G17">
-        <v>0.2628</v>
+        <v>0.4609</v>
       </c>
       <c r="H17">
-        <v>0.5541</v>
+        <v>0.4449</v>
       </c>
       <c r="I17">
-        <v>0.3383</v>
-      </c>
-      <c r="J17" t="s">
-        <v>49</v>
-      </c>
-      <c r="K17" t="s">
-        <v>50</v>
+        <v>0.2702</v>
+      </c>
+      <c r="J17">
+        <v>0.2463</v>
+      </c>
+      <c r="K17">
+        <v>0.4913</v>
       </c>
       <c r="L17">
-        <v>0.5027</v>
+        <v>0.3365</v>
       </c>
       <c r="M17">
-        <v>0.5842</v>
-      </c>
-      <c r="N17">
-        <v>0.2993</v>
+        <v>0.1924</v>
+      </c>
+      <c r="N17" t="s">
+        <v>53</v>
       </c>
       <c r="O17">
-        <v>0.5482</v>
-      </c>
-      <c r="P17" t="s">
-        <v>51</v>
+        <v>0.3372</v>
+      </c>
+      <c r="P17">
+        <v>0.294</v>
       </c>
       <c r="Q17">
-        <v>0.3394</v>
+        <v>0.2163</v>
       </c>
       <c r="R17">
-        <v>0.5828</v>
+        <v>0.2177</v>
       </c>
       <c r="S17">
-        <v>0.4412</v>
+        <v>0.2138</v>
       </c>
       <c r="T17">
-        <v>0.5823</v>
-      </c>
-      <c r="U17">
-        <v>0.4137</v>
-      </c>
-      <c r="V17">
-        <v>0.3706</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18">
-        <v>0.3219</v>
-      </c>
-      <c r="C18">
-        <v>0.2074</v>
-      </c>
-      <c r="D18">
-        <v>0.3037</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0.271</v>
-      </c>
-      <c r="G18">
-        <v>0.4609</v>
-      </c>
-      <c r="H18">
-        <v>0.4449</v>
-      </c>
-      <c r="I18">
-        <v>0.2702</v>
-      </c>
-      <c r="J18">
-        <v>0.2463</v>
-      </c>
-      <c r="K18">
-        <v>0.4913</v>
-      </c>
-      <c r="L18">
-        <v>0.3365</v>
-      </c>
-      <c r="M18">
-        <v>0.1924</v>
-      </c>
-      <c r="N18" t="s">
-        <v>53</v>
-      </c>
-      <c r="O18">
-        <v>0.3372</v>
-      </c>
-      <c r="P18">
-        <v>0.294</v>
-      </c>
-      <c r="Q18">
-        <v>0.2163</v>
-      </c>
-      <c r="R18">
-        <v>0.2177</v>
-      </c>
-      <c r="S18">
-        <v>0.2138</v>
-      </c>
-      <c r="T18">
         <v>0.1716</v>
       </c>
-      <c r="U18" t="s">
+      <c r="U17" t="s">
         <v>54</v>
       </c>
-      <c r="V18" t="s">
+      <c r="V17" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2177,14 +2238,98 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2199,87 +2344,87 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>57</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -3078,8 +3223,92 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC13" s="1" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3094,87 +3323,87 @@
         <v>3</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W14" s="2" t="s">
         <v>57</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="AA14" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
@@ -3973,8 +4202,92 @@
         <v>0.1008</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC25" s="1" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3989,87 +4302,87 @@
         <v>3</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V26" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W26" s="2" t="s">
         <v>57</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="AA26" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -4868,8 +5181,92 @@
         <v>0.1135</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC37" s="1" t="s">
         <v>169</v>
       </c>
     </row>
@@ -4884,87 +5281,87 @@
         <v>3</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>57</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AB38" s="2" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="AC38" s="2" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -5053,1519 +5450,1514 @@
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B40">
-        <v>2610</v>
+        <v>2530</v>
       </c>
       <c r="C40">
-        <v>1279</v>
+        <v>1272</v>
       </c>
       <c r="D40">
-        <v>1331</v>
+        <v>1291</v>
       </c>
       <c r="E40">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F40">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G40">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="H40">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="I40">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="J40">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="K40">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="L40">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="M40">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="N40">
-        <v>964</v>
+        <v>913</v>
       </c>
       <c r="O40">
-        <v>1373</v>
+        <v>1411</v>
       </c>
       <c r="P40">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="Q40">
-        <v>611</v>
+        <v>626</v>
       </c>
       <c r="R40">
-        <v>803</v>
+        <v>792</v>
       </c>
       <c r="S40">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="T40">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="U40">
-        <v>1189</v>
+        <v>1250</v>
       </c>
       <c r="V40">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="W40">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X40">
         <v>63</v>
       </c>
       <c r="Y40">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Z40">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="AA40">
-        <v>2611</v>
+        <v>2727</v>
       </c>
       <c r="AB40">
-        <v>2044</v>
+        <v>2011</v>
       </c>
       <c r="AC40">
-        <v>1188</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="B41">
-        <v>2530</v>
+        <v>0.6645</v>
       </c>
       <c r="C41">
-        <v>1272</v>
-      </c>
-      <c r="D41">
-        <v>1291</v>
-      </c>
-      <c r="E41">
-        <v>175</v>
+        <v>0.646</v>
+      </c>
+      <c r="D41" t="s">
+        <v>171</v>
+      </c>
+      <c r="E41" t="s">
+        <v>172</v>
       </c>
       <c r="F41">
-        <v>285</v>
+        <v>0.7683</v>
       </c>
       <c r="G41">
-        <v>405</v>
+        <v>0.5031</v>
       </c>
       <c r="H41">
-        <v>441</v>
+        <v>0.6905</v>
       </c>
       <c r="I41">
-        <v>403</v>
+        <v>0.7063</v>
       </c>
       <c r="J41">
-        <v>423</v>
+        <v>0.6451</v>
       </c>
       <c r="K41">
-        <v>409</v>
+        <v>0.7508</v>
       </c>
       <c r="L41">
-        <v>211</v>
+        <v>0.5323</v>
       </c>
       <c r="M41">
-        <v>181</v>
+        <v>0.5164</v>
       </c>
       <c r="N41">
-        <v>913</v>
-      </c>
-      <c r="O41">
-        <v>1411</v>
+        <v>0.6926</v>
+      </c>
+      <c r="O41" t="s">
+        <v>173</v>
       </c>
       <c r="P41">
-        <v>741</v>
+        <v>0.5411</v>
       </c>
       <c r="Q41">
-        <v>626</v>
+        <v>0.5829</v>
       </c>
       <c r="R41">
-        <v>792</v>
+        <v>0.741</v>
       </c>
       <c r="S41">
-        <v>377</v>
+        <v>0.7622</v>
       </c>
       <c r="T41">
-        <v>1111</v>
+        <v>0.8256</v>
       </c>
       <c r="U41">
-        <v>1250</v>
+        <v>0.7581</v>
       </c>
       <c r="V41">
-        <v>221</v>
+        <v>0.7773</v>
       </c>
       <c r="W41">
-        <v>26</v>
+        <v>0.534</v>
       </c>
       <c r="X41">
-        <v>63</v>
+        <v>0.5232</v>
       </c>
       <c r="Y41">
-        <v>75</v>
+        <v>0.5503</v>
       </c>
       <c r="Z41">
-        <v>123</v>
+        <v>0.6416</v>
       </c>
       <c r="AA41">
-        <v>2727</v>
+        <v>0.6257</v>
       </c>
       <c r="AB41">
-        <v>2011</v>
-      </c>
-      <c r="AC41">
-        <v>1120</v>
+        <v>0.6432</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B42">
-        <v>0.6645</v>
+        <v>0.5157</v>
       </c>
       <c r="C42">
-        <v>0.646</v>
-      </c>
-      <c r="D42" t="s">
-        <v>171</v>
+        <v>0.38</v>
+      </c>
+      <c r="D42">
+        <v>0.5649</v>
       </c>
       <c r="E42" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F42">
-        <v>0.7683</v>
+        <v>0.498</v>
       </c>
       <c r="G42">
-        <v>0.5031</v>
-      </c>
-      <c r="H42">
-        <v>0.6905</v>
+        <v>0.5484</v>
+      </c>
+      <c r="H42" t="s">
+        <v>177</v>
       </c>
       <c r="I42">
-        <v>0.7063</v>
+        <v>0.6602</v>
       </c>
       <c r="J42">
-        <v>0.6451</v>
+        <v>0.5225</v>
       </c>
       <c r="K42">
-        <v>0.7508</v>
+        <v>0.6382</v>
       </c>
       <c r="L42">
-        <v>0.5323</v>
+        <v>0.416</v>
       </c>
       <c r="M42">
-        <v>0.5164</v>
+        <v>0.4753</v>
       </c>
       <c r="N42">
-        <v>0.6926</v>
-      </c>
-      <c r="O42" t="s">
-        <v>173</v>
+        <v>0.4738</v>
+      </c>
+      <c r="O42">
+        <v>0.5557</v>
       </c>
       <c r="P42">
-        <v>0.5411</v>
+        <v>0.3874</v>
       </c>
       <c r="Q42">
-        <v>0.5829</v>
+        <v>0.6724</v>
       </c>
       <c r="R42">
-        <v>0.741</v>
+        <v>0.6856</v>
       </c>
       <c r="S42">
-        <v>0.7622</v>
+        <v>0.3766</v>
       </c>
       <c r="T42">
-        <v>0.8256</v>
-      </c>
-      <c r="U42">
-        <v>0.7581</v>
-      </c>
-      <c r="V42">
-        <v>0.7773</v>
+        <v>0.378</v>
+      </c>
+      <c r="U42" t="s">
+        <v>178</v>
+      </c>
+      <c r="V42" t="s">
+        <v>179</v>
       </c>
       <c r="W42">
-        <v>0.534</v>
+        <v>0.631</v>
       </c>
       <c r="X42">
-        <v>0.5232</v>
+        <v>0.6001</v>
       </c>
       <c r="Y42">
-        <v>0.5503</v>
+        <v>0.4145</v>
       </c>
       <c r="Z42">
-        <v>0.6416</v>
+        <v>0.4685</v>
       </c>
       <c r="AA42">
-        <v>0.6257</v>
+        <v>0.622</v>
       </c>
       <c r="AB42">
-        <v>0.6432</v>
+        <v>0.4772</v>
       </c>
       <c r="AC42" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B43">
-        <v>0.5157</v>
+        <v>0.4491</v>
       </c>
       <c r="C43">
-        <v>0.38</v>
-      </c>
-      <c r="D43">
-        <v>0.5649</v>
-      </c>
-      <c r="E43" t="s">
-        <v>176</v>
+        <v>0.6008</v>
+      </c>
+      <c r="D43" t="s">
+        <v>182</v>
+      </c>
+      <c r="E43">
+        <v>0.2941</v>
       </c>
       <c r="F43">
-        <v>0.498</v>
+        <v>0.4468</v>
       </c>
       <c r="G43">
-        <v>0.5484</v>
+        <v>0.33</v>
       </c>
       <c r="H43" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I43">
-        <v>0.6602</v>
+        <v>0.3993</v>
       </c>
       <c r="J43">
-        <v>0.5225</v>
-      </c>
-      <c r="K43">
-        <v>0.6382</v>
+        <v>0.4541</v>
+      </c>
+      <c r="K43" t="s">
+        <v>184</v>
       </c>
       <c r="L43">
-        <v>0.416</v>
+        <v>0.4132</v>
       </c>
       <c r="M43">
-        <v>0.4753</v>
+        <v>0.3455</v>
       </c>
       <c r="N43">
-        <v>0.4738</v>
+        <v>0.5598</v>
       </c>
       <c r="O43">
-        <v>0.5557</v>
+        <v>0.3025</v>
       </c>
       <c r="P43">
-        <v>0.3874</v>
+        <v>0.4053</v>
       </c>
       <c r="Q43">
-        <v>0.6724</v>
+        <v>0.5071</v>
       </c>
       <c r="R43">
-        <v>0.6856</v>
+        <v>0.4828</v>
       </c>
       <c r="S43">
-        <v>0.3766</v>
+        <v>0.5448</v>
       </c>
       <c r="T43">
-        <v>0.378</v>
+        <v>0.3932</v>
       </c>
       <c r="U43" t="s">
-        <v>178</v>
-      </c>
-      <c r="V43" t="s">
-        <v>179</v>
+        <v>185</v>
+      </c>
+      <c r="V43">
+        <v>0.5745</v>
       </c>
       <c r="W43">
-        <v>0.631</v>
+        <v>0.3148</v>
       </c>
       <c r="X43">
-        <v>0.6001</v>
+        <v>0.5318</v>
       </c>
       <c r="Y43">
-        <v>0.4145</v>
+        <v>0.414</v>
       </c>
       <c r="Z43">
-        <v>0.4685</v>
+        <v>0.4527</v>
       </c>
       <c r="AA43">
-        <v>0.622</v>
+        <v>0.5504</v>
       </c>
       <c r="AB43">
-        <v>0.4772</v>
-      </c>
-      <c r="AC43" t="s">
-        <v>180</v>
+        <v>0.3914</v>
+      </c>
+      <c r="AC43">
+        <v>0.4573</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B44">
-        <v>0.4491</v>
+        <v>0.3284</v>
       </c>
       <c r="C44">
-        <v>0.6008</v>
-      </c>
-      <c r="D44" t="s">
-        <v>182</v>
+        <v>0.3037</v>
+      </c>
+      <c r="D44">
+        <v>0.32</v>
       </c>
       <c r="E44">
-        <v>0.2941</v>
+        <v>0.3792</v>
       </c>
       <c r="F44">
-        <v>0.4468</v>
+        <v>0.4269</v>
       </c>
       <c r="G44">
-        <v>0.33</v>
-      </c>
-      <c r="H44" t="s">
-        <v>183</v>
+        <v>0.3489</v>
+      </c>
+      <c r="H44">
+        <v>0.1733</v>
       </c>
       <c r="I44">
-        <v>0.3993</v>
+        <v>0.2833</v>
       </c>
       <c r="J44">
-        <v>0.4541</v>
+        <v>0.3544</v>
       </c>
       <c r="K44" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L44">
-        <v>0.4132</v>
-      </c>
-      <c r="M44">
-        <v>0.3455</v>
+        <v>0.3049</v>
+      </c>
+      <c r="M44" t="s">
+        <v>188</v>
       </c>
       <c r="N44">
-        <v>0.5598</v>
+        <v>0.2928</v>
       </c>
       <c r="O44">
-        <v>0.3025</v>
-      </c>
-      <c r="P44">
-        <v>0.4053</v>
-      </c>
-      <c r="Q44">
-        <v>0.5071</v>
+        <v>0.4359</v>
+      </c>
+      <c r="P44" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>190</v>
       </c>
       <c r="R44">
-        <v>0.4828</v>
+        <v>0.236</v>
       </c>
       <c r="S44">
-        <v>0.5448</v>
+        <v>0.4863</v>
       </c>
       <c r="T44">
-        <v>0.3932</v>
-      </c>
-      <c r="U44" t="s">
-        <v>185</v>
+        <v>0.2353</v>
+      </c>
+      <c r="U44">
+        <v>0.2918</v>
       </c>
       <c r="V44">
-        <v>0.5745</v>
-      </c>
-      <c r="W44">
-        <v>0.3148</v>
+        <v>0.3426</v>
+      </c>
+      <c r="W44" t="s">
+        <v>191</v>
       </c>
       <c r="X44">
-        <v>0.5318</v>
+        <v>0.1936</v>
       </c>
       <c r="Y44">
-        <v>0.414</v>
-      </c>
-      <c r="Z44">
-        <v>0.4527</v>
+        <v>0.39</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>192</v>
       </c>
       <c r="AA44">
-        <v>0.5504</v>
+        <v>0.4111</v>
       </c>
       <c r="AB44">
-        <v>0.3914</v>
-      </c>
-      <c r="AC44">
-        <v>0.4573</v>
+        <v>0.2917</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B45">
-        <v>0.3284</v>
+        <v>0.2077</v>
       </c>
       <c r="C45">
-        <v>0.3037</v>
-      </c>
-      <c r="D45">
-        <v>0.32</v>
+        <v>0.1725</v>
+      </c>
+      <c r="D45" t="s">
+        <v>195</v>
       </c>
       <c r="E45">
-        <v>0.3792</v>
-      </c>
-      <c r="F45">
-        <v>0.4269</v>
-      </c>
-      <c r="G45">
-        <v>0.3489</v>
+        <v>0.277</v>
+      </c>
+      <c r="F45" t="s">
+        <v>196</v>
+      </c>
+      <c r="G45" t="s">
+        <v>197</v>
       </c>
       <c r="H45">
-        <v>0.1733</v>
+        <v>0.1161</v>
       </c>
       <c r="I45">
-        <v>0.2833</v>
+        <v>0.3283</v>
       </c>
       <c r="J45">
-        <v>0.3544</v>
-      </c>
-      <c r="K45" t="s">
-        <v>187</v>
+        <v>0.2953</v>
+      </c>
+      <c r="K45">
+        <v>0.1606</v>
       </c>
       <c r="L45">
-        <v>0.3049</v>
-      </c>
-      <c r="M45" t="s">
-        <v>188</v>
+        <v>0.2455</v>
+      </c>
+      <c r="M45">
+        <v>0.3401</v>
       </c>
       <c r="N45">
-        <v>0.2928</v>
+        <v>0.0404</v>
       </c>
       <c r="O45">
-        <v>0.4359</v>
+        <v>0.2555</v>
       </c>
       <c r="P45" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>190</v>
+        <v>198</v>
+      </c>
+      <c r="Q45">
+        <v>0.3275</v>
       </c>
       <c r="R45">
-        <v>0.236</v>
+        <v>0.0771</v>
       </c>
       <c r="S45">
-        <v>0.4863</v>
+        <v>0.1994</v>
       </c>
       <c r="T45">
-        <v>0.2353</v>
+        <v>0.1283</v>
       </c>
       <c r="U45">
-        <v>0.2918</v>
+        <v>0.3518</v>
       </c>
       <c r="V45">
-        <v>0.3426</v>
-      </c>
-      <c r="W45" t="s">
-        <v>191</v>
+        <v>0.1538</v>
+      </c>
+      <c r="W45">
+        <v>0.2836</v>
       </c>
       <c r="X45">
-        <v>0.1936</v>
+        <v>0.0854</v>
       </c>
       <c r="Y45">
-        <v>0.39</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>192</v>
+        <v>0.1235</v>
+      </c>
+      <c r="Z45">
+        <v>0.2905</v>
       </c>
       <c r="AA45">
-        <v>0.4111</v>
-      </c>
-      <c r="AB45">
-        <v>0.2917</v>
+        <v>0.0489</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>199</v>
       </c>
       <c r="AC45" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>194</v>
-      </c>
-      <c r="B46">
-        <v>0.2077</v>
-      </c>
-      <c r="C46">
-        <v>0.1725</v>
-      </c>
-      <c r="D46" t="s">
-        <v>195</v>
-      </c>
-      <c r="E46">
-        <v>0.277</v>
-      </c>
-      <c r="F46" t="s">
-        <v>196</v>
-      </c>
-      <c r="G46" t="s">
-        <v>197</v>
-      </c>
-      <c r="H46">
-        <v>0.1161</v>
-      </c>
-      <c r="I46">
-        <v>0.3283</v>
-      </c>
-      <c r="J46">
-        <v>0.2953</v>
-      </c>
-      <c r="K46">
-        <v>0.1606</v>
-      </c>
-      <c r="L46">
-        <v>0.2455</v>
-      </c>
-      <c r="M46">
-        <v>0.3401</v>
-      </c>
-      <c r="N46">
-        <v>0.0404</v>
-      </c>
-      <c r="O46">
-        <v>0.2555</v>
-      </c>
-      <c r="P46" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q46">
-        <v>0.3275</v>
-      </c>
-      <c r="R46">
-        <v>0.0771</v>
-      </c>
-      <c r="S46">
-        <v>0.1994</v>
-      </c>
-      <c r="T46">
-        <v>0.1283</v>
-      </c>
-      <c r="U46">
-        <v>0.3518</v>
-      </c>
-      <c r="V46">
-        <v>0.1538</v>
-      </c>
-      <c r="W46">
-        <v>0.2836</v>
-      </c>
-      <c r="X46">
-        <v>0.0854</v>
-      </c>
-      <c r="Y46">
-        <v>0.1235</v>
-      </c>
-      <c r="Z46">
-        <v>0.2905</v>
-      </c>
-      <c r="AA46">
-        <v>0.0489</v>
-      </c>
-      <c r="AB46" t="s">
-        <v>199</v>
-      </c>
-      <c r="AC46" t="s">
-        <v>200</v>
+    <row r="47" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="R47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="S47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="W47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="X47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AB47" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AC47" s="1" t="s">
+        <v>201</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>201</v>
+    <row r="48" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC48" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="S49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="T49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="U49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="V49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="W49" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="X49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA49" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC49" s="2" t="s">
-        <v>2</v>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" t="s">
+        <v>15</v>
+      </c>
+      <c r="J49" t="s">
+        <v>16</v>
+      </c>
+      <c r="K49" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49" t="s">
+        <v>18</v>
+      </c>
+      <c r="M49" t="s">
+        <v>19</v>
+      </c>
+      <c r="N49" t="s">
+        <v>20</v>
+      </c>
+      <c r="O49" t="s">
+        <v>21</v>
+      </c>
+      <c r="P49" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>23</v>
+      </c>
+      <c r="R49" t="s">
+        <v>24</v>
+      </c>
+      <c r="S49" t="s">
+        <v>25</v>
+      </c>
+      <c r="T49" t="s">
+        <v>26</v>
+      </c>
+      <c r="U49" t="s">
+        <v>27</v>
+      </c>
+      <c r="V49" t="s">
+        <v>28</v>
+      </c>
+      <c r="W49" t="s">
+        <v>59</v>
+      </c>
+      <c r="X49" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" t="s">
-        <v>12</v>
-      </c>
-      <c r="G50" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" t="s">
-        <v>14</v>
-      </c>
-      <c r="I50" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" t="s">
-        <v>16</v>
-      </c>
-      <c r="K50" t="s">
-        <v>17</v>
-      </c>
-      <c r="L50" t="s">
-        <v>18</v>
-      </c>
-      <c r="M50" t="s">
-        <v>19</v>
-      </c>
-      <c r="N50" t="s">
-        <v>20</v>
-      </c>
-      <c r="O50" t="s">
-        <v>21</v>
-      </c>
-      <c r="P50" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>23</v>
-      </c>
-      <c r="R50" t="s">
-        <v>24</v>
-      </c>
-      <c r="S50" t="s">
-        <v>25</v>
-      </c>
-      <c r="T50" t="s">
-        <v>26</v>
-      </c>
-      <c r="U50" t="s">
-        <v>27</v>
-      </c>
-      <c r="V50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50">
+        <v>2725</v>
+      </c>
+      <c r="C50">
+        <v>1335</v>
+      </c>
+      <c r="D50">
+        <v>1390</v>
+      </c>
+      <c r="E50">
+        <v>174</v>
+      </c>
+      <c r="F50">
+        <v>289</v>
+      </c>
+      <c r="G50">
+        <v>402</v>
+      </c>
+      <c r="H50">
+        <v>431</v>
+      </c>
+      <c r="I50">
+        <v>397</v>
+      </c>
+      <c r="J50">
+        <v>412</v>
+      </c>
+      <c r="K50">
+        <v>388</v>
+      </c>
+      <c r="L50">
+        <v>206</v>
+      </c>
+      <c r="M50">
+        <v>188</v>
+      </c>
+      <c r="N50">
+        <v>964</v>
+      </c>
+      <c r="O50">
+        <v>1373</v>
+      </c>
+      <c r="P50">
+        <v>742</v>
+      </c>
+      <c r="Q50">
+        <v>611</v>
+      </c>
+      <c r="R50">
+        <v>803</v>
+      </c>
+      <c r="S50">
+        <v>369</v>
+      </c>
+      <c r="T50">
+        <v>1104</v>
+      </c>
+      <c r="U50">
+        <v>1189</v>
+      </c>
+      <c r="V50">
+        <v>232</v>
+      </c>
+      <c r="W50">
         <v>28</v>
       </c>
-      <c r="W50" t="s">
-        <v>59</v>
-      </c>
-      <c r="X50" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA50" t="s">
+      <c r="X50">
         <v>63</v>
       </c>
-      <c r="AB50" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC50" t="s">
-        <v>65</v>
+      <c r="Y50">
+        <v>71</v>
+      </c>
+      <c r="Z50">
+        <v>118</v>
+      </c>
+      <c r="AA50">
+        <v>2611</v>
+      </c>
+      <c r="AB50">
+        <v>2044</v>
+      </c>
+      <c r="AC50">
+        <v>1188</v>
       </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B51">
-        <v>2725</v>
+        <v>2642</v>
       </c>
       <c r="C51">
-        <v>1335</v>
+        <v>1342</v>
       </c>
       <c r="D51">
-        <v>1390</v>
+        <v>1463</v>
       </c>
       <c r="E51">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F51">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="G51">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="H51">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="I51">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J51">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="K51">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="L51">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="M51">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N51">
-        <v>964</v>
+        <v>910</v>
       </c>
       <c r="O51">
-        <v>1373</v>
+        <v>1403</v>
       </c>
       <c r="P51">
-        <v>742</v>
+        <v>761</v>
       </c>
       <c r="Q51">
-        <v>611</v>
+        <v>587</v>
       </c>
       <c r="R51">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="S51">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="T51">
-        <v>1104</v>
+        <v>1150</v>
       </c>
       <c r="U51">
-        <v>1189</v>
+        <v>1234</v>
       </c>
       <c r="V51">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="W51">
         <v>28</v>
       </c>
       <c r="X51">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="Y51">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Z51">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="AA51">
-        <v>2611</v>
+        <v>2552</v>
       </c>
       <c r="AB51">
-        <v>2044</v>
+        <v>2158</v>
       </c>
       <c r="AC51">
-        <v>1188</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>202</v>
       </c>
       <c r="B52">
-        <v>2642</v>
-      </c>
-      <c r="C52">
-        <v>1342</v>
+        <v>0.655</v>
+      </c>
+      <c r="C52" t="s">
+        <v>203</v>
       </c>
       <c r="D52">
-        <v>1463</v>
+        <v>0.7997</v>
       </c>
       <c r="E52">
-        <v>176</v>
+        <v>0.4931</v>
       </c>
       <c r="F52">
-        <v>273</v>
+        <v>0.6338</v>
       </c>
       <c r="G52">
-        <v>393</v>
+        <v>0.6678</v>
       </c>
       <c r="H52">
-        <v>411</v>
+        <v>0.6839</v>
       </c>
       <c r="I52">
-        <v>399</v>
-      </c>
-      <c r="J52">
-        <v>398</v>
+        <v>0.5464</v>
+      </c>
+      <c r="J52" t="s">
+        <v>204</v>
       </c>
       <c r="K52">
-        <v>366</v>
-      </c>
-      <c r="L52">
-        <v>197</v>
+        <v>0.8067</v>
+      </c>
+      <c r="L52" t="s">
+        <v>205</v>
       </c>
       <c r="M52">
-        <v>196</v>
+        <v>0.6713</v>
       </c>
       <c r="N52">
-        <v>910</v>
+        <v>0.7154</v>
       </c>
       <c r="O52">
-        <v>1403</v>
+        <v>0.5998</v>
       </c>
       <c r="P52">
-        <v>761</v>
+        <v>0.5315</v>
       </c>
       <c r="Q52">
-        <v>587</v>
+        <v>0.6838</v>
       </c>
       <c r="R52">
-        <v>807</v>
-      </c>
-      <c r="S52">
-        <v>377</v>
-      </c>
-      <c r="T52">
-        <v>1150</v>
+        <v>0.6386</v>
+      </c>
+      <c r="S52" t="s">
+        <v>206</v>
+      </c>
+      <c r="T52" t="s">
+        <v>207</v>
       </c>
       <c r="U52">
-        <v>1234</v>
+        <v>0.6827</v>
       </c>
       <c r="V52">
-        <v>240</v>
+        <v>0.5164</v>
       </c>
       <c r="W52">
-        <v>28</v>
+        <v>0.7999</v>
       </c>
       <c r="X52">
-        <v>60</v>
+        <v>0.6748</v>
       </c>
       <c r="Y52">
-        <v>67</v>
+        <v>0.7487</v>
       </c>
       <c r="Z52">
-        <v>124</v>
+        <v>0.5523</v>
       </c>
       <c r="AA52">
-        <v>2552</v>
-      </c>
-      <c r="AB52">
-        <v>2158</v>
+        <v>0.5998</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>208</v>
       </c>
       <c r="AC52">
-        <v>1229</v>
+        <v>0.7077</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B53">
-        <v>0.655</v>
+        <v>0.5487</v>
       </c>
       <c r="C53" t="s">
-        <v>203</v>
-      </c>
-      <c r="D53">
-        <v>0.7997</v>
+        <v>210</v>
+      </c>
+      <c r="D53" t="s">
+        <v>211</v>
       </c>
       <c r="E53">
-        <v>0.4931</v>
-      </c>
-      <c r="F53">
-        <v>0.6338</v>
+        <v>0.3931</v>
+      </c>
+      <c r="F53" t="s">
+        <v>212</v>
       </c>
       <c r="G53">
-        <v>0.6678</v>
+        <v>0.5546</v>
       </c>
       <c r="H53">
-        <v>0.6839</v>
-      </c>
-      <c r="I53">
-        <v>0.5464</v>
-      </c>
-      <c r="J53" t="s">
-        <v>204</v>
+        <v>0.6473</v>
+      </c>
+      <c r="I53" t="s">
+        <v>213</v>
+      </c>
+      <c r="J53">
+        <v>0.4887</v>
       </c>
       <c r="K53">
-        <v>0.8067</v>
-      </c>
-      <c r="L53" t="s">
-        <v>205</v>
-      </c>
-      <c r="M53">
-        <v>0.6713</v>
+        <v>0.5248</v>
+      </c>
+      <c r="L53">
+        <v>0.6438</v>
+      </c>
+      <c r="M53" t="s">
+        <v>214</v>
       </c>
       <c r="N53">
-        <v>0.7154</v>
+        <v>0.4929</v>
       </c>
       <c r="O53">
-        <v>0.5998</v>
+        <v>0.5599</v>
       </c>
       <c r="P53">
-        <v>0.5315</v>
+        <v>0.5926</v>
       </c>
       <c r="Q53">
-        <v>0.6838</v>
+        <v>0.5789</v>
       </c>
       <c r="R53">
-        <v>0.6386</v>
-      </c>
-      <c r="S53" t="s">
-        <v>206</v>
-      </c>
-      <c r="T53" t="s">
-        <v>207</v>
+        <v>0.5457</v>
+      </c>
+      <c r="S53">
+        <v>0.5318</v>
+      </c>
+      <c r="T53">
+        <v>0.591</v>
       </c>
       <c r="U53">
-        <v>0.6827</v>
-      </c>
-      <c r="V53">
-        <v>0.5164</v>
+        <v>0.3843</v>
+      </c>
+      <c r="V53" t="s">
+        <v>215</v>
       </c>
       <c r="W53">
-        <v>0.7999</v>
+        <v>0.5777</v>
       </c>
       <c r="X53">
-        <v>0.6748</v>
+        <v>0.4091</v>
       </c>
       <c r="Y53">
-        <v>0.7487</v>
+        <v>0.4163</v>
       </c>
       <c r="Z53">
-        <v>0.5523</v>
+        <v>0.5403</v>
       </c>
       <c r="AA53">
-        <v>0.5998</v>
-      </c>
-      <c r="AB53" t="s">
-        <v>208</v>
+        <v>0.6939</v>
+      </c>
+      <c r="AB53">
+        <v>0.4676</v>
       </c>
       <c r="AC53">
-        <v>0.7077</v>
+        <v>0.6541</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B54">
-        <v>0.5487</v>
-      </c>
-      <c r="C54" t="s">
-        <v>210</v>
-      </c>
-      <c r="D54" t="s">
-        <v>211</v>
+        <v>0.4199</v>
+      </c>
+      <c r="C54">
+        <v>0.5805</v>
+      </c>
+      <c r="D54">
+        <v>0.2939</v>
       </c>
       <c r="E54">
-        <v>0.3931</v>
-      </c>
-      <c r="F54" t="s">
-        <v>212</v>
+        <v>0.3236</v>
+      </c>
+      <c r="F54">
+        <v>0.2969</v>
       </c>
       <c r="G54">
-        <v>0.5546</v>
-      </c>
-      <c r="H54">
-        <v>0.6473</v>
+        <v>0.253</v>
+      </c>
+      <c r="H54" t="s">
+        <v>217</v>
       </c>
       <c r="I54" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="J54">
-        <v>0.4887</v>
+        <v>0.5214</v>
       </c>
       <c r="K54">
-        <v>0.5248</v>
+        <v>0.4517</v>
       </c>
       <c r="L54">
-        <v>0.6438</v>
-      </c>
-      <c r="M54" t="s">
-        <v>214</v>
+        <v>0.407</v>
+      </c>
+      <c r="M54">
+        <v>0.2698</v>
       </c>
       <c r="N54">
-        <v>0.4929</v>
+        <v>0.3249</v>
       </c>
       <c r="O54">
-        <v>0.5599</v>
+        <v>0.2686</v>
       </c>
       <c r="P54">
-        <v>0.5926</v>
+        <v>0.4829</v>
       </c>
       <c r="Q54">
-        <v>0.5789</v>
+        <v>0.3706</v>
       </c>
       <c r="R54">
-        <v>0.5457</v>
+        <v>0.3471</v>
       </c>
       <c r="S54">
-        <v>0.5318</v>
+        <v>0.4862</v>
       </c>
       <c r="T54">
-        <v>0.591</v>
+        <v>0.4273</v>
       </c>
       <c r="U54">
-        <v>0.3843</v>
-      </c>
-      <c r="V54" t="s">
-        <v>215</v>
+        <v>0.2537</v>
+      </c>
+      <c r="V54">
+        <v>0.2975</v>
       </c>
       <c r="W54">
-        <v>0.5777</v>
+        <v>0.3518</v>
       </c>
       <c r="X54">
-        <v>0.4091</v>
+        <v>0.4014</v>
       </c>
       <c r="Y54">
-        <v>0.4163</v>
+        <v>0.3943</v>
       </c>
       <c r="Z54">
-        <v>0.5403</v>
+        <v>0.315</v>
       </c>
       <c r="AA54">
-        <v>0.6939</v>
+        <v>0.4049</v>
       </c>
       <c r="AB54">
-        <v>0.4676</v>
-      </c>
-      <c r="AC54">
-        <v>0.6541</v>
+        <v>0.507</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B55">
-        <v>0.4199</v>
+        <v>0.2968</v>
       </c>
       <c r="C55">
-        <v>0.5805</v>
+        <v>0.4425</v>
       </c>
       <c r="D55">
-        <v>0.2939</v>
-      </c>
-      <c r="E55">
-        <v>0.3236</v>
+        <v>0.3638</v>
+      </c>
+      <c r="E55" t="s">
+        <v>221</v>
       </c>
       <c r="F55">
-        <v>0.2969</v>
+        <v>0.2224</v>
       </c>
       <c r="G55">
-        <v>0.253</v>
+        <v>0.4587</v>
       </c>
       <c r="H55" t="s">
-        <v>217</v>
-      </c>
-      <c r="I55" t="s">
-        <v>218</v>
+        <v>222</v>
+      </c>
+      <c r="I55">
+        <v>0.4514</v>
       </c>
       <c r="J55">
-        <v>0.5214</v>
+        <v>0.3918</v>
       </c>
       <c r="K55">
-        <v>0.4517</v>
+        <v>0.3265</v>
       </c>
       <c r="L55">
-        <v>0.407</v>
+        <v>0.4595</v>
       </c>
       <c r="M55">
-        <v>0.2698</v>
+        <v>0.1955</v>
       </c>
       <c r="N55">
-        <v>0.3249</v>
+        <v>0.4352</v>
       </c>
       <c r="O55">
-        <v>0.2686</v>
+        <v>0.4016</v>
       </c>
       <c r="P55">
-        <v>0.4829</v>
-      </c>
-      <c r="Q55">
-        <v>0.3706</v>
+        <v>0.2373</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>223</v>
       </c>
       <c r="R55">
-        <v>0.3471</v>
+        <v>0.1763</v>
       </c>
       <c r="S55">
-        <v>0.4862</v>
+        <v>0.239</v>
       </c>
       <c r="T55">
-        <v>0.4273</v>
+        <v>0.4414</v>
       </c>
       <c r="U55">
-        <v>0.2537</v>
+        <v>0.1956</v>
       </c>
       <c r="V55">
-        <v>0.2975</v>
+        <v>0.4259</v>
       </c>
       <c r="W55">
-        <v>0.3518</v>
+        <v>0.1736</v>
       </c>
       <c r="X55">
-        <v>0.4014</v>
+        <v>0.2846</v>
       </c>
       <c r="Y55">
-        <v>0.3943</v>
+        <v>0.1514</v>
       </c>
       <c r="Z55">
-        <v>0.315</v>
+        <v>0.4271</v>
       </c>
       <c r="AA55">
-        <v>0.4049</v>
+        <v>0.1763</v>
       </c>
       <c r="AB55">
-        <v>0.507</v>
+        <v>0.2873</v>
       </c>
       <c r="AC55" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B56">
-        <v>0.2968</v>
-      </c>
-      <c r="C56">
-        <v>0.4425</v>
+        <v>0.1846</v>
+      </c>
+      <c r="C56" t="s">
+        <v>226</v>
       </c>
       <c r="D56">
-        <v>0.3638</v>
-      </c>
-      <c r="E56" t="s">
-        <v>221</v>
+        <v>0.0631</v>
+      </c>
+      <c r="E56">
+        <v>0.3392</v>
       </c>
       <c r="F56">
-        <v>0.2224</v>
-      </c>
-      <c r="G56">
-        <v>0.4587</v>
-      </c>
-      <c r="H56" t="s">
-        <v>222</v>
+        <v>0.2832</v>
+      </c>
+      <c r="G56" t="s">
+        <v>227</v>
+      </c>
+      <c r="H56">
+        <v>0.2418</v>
       </c>
       <c r="I56">
-        <v>0.4514</v>
+        <v>0.0417</v>
       </c>
       <c r="J56">
-        <v>0.3918</v>
-      </c>
-      <c r="K56">
-        <v>0.3265</v>
+        <v>0.2204</v>
+      </c>
+      <c r="K56" t="s">
+        <v>228</v>
       </c>
       <c r="L56">
-        <v>0.4595</v>
+        <v>0.0373</v>
       </c>
       <c r="M56">
-        <v>0.1955</v>
+        <v>0.2799</v>
       </c>
       <c r="N56">
-        <v>0.4352</v>
+        <v>0.1913</v>
       </c>
       <c r="O56">
-        <v>0.4016</v>
+        <v>0.0526</v>
       </c>
       <c r="P56">
-        <v>0.2373</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>223</v>
+        <v>0.2443</v>
+      </c>
+      <c r="Q56">
+        <v>0.1743</v>
       </c>
       <c r="R56">
-        <v>0.1763</v>
+        <v>0.1317</v>
       </c>
       <c r="S56">
-        <v>0.239</v>
+        <v>0.1058</v>
       </c>
       <c r="T56">
-        <v>0.4414</v>
+        <v>0.0285</v>
       </c>
       <c r="U56">
-        <v>0.1956</v>
+        <v>0.1501</v>
       </c>
       <c r="V56">
-        <v>0.4259</v>
+        <v>0.038</v>
       </c>
       <c r="W56">
-        <v>0.1736</v>
+        <v>0.0967</v>
       </c>
       <c r="X56">
-        <v>0.2846</v>
+        <v>0.0949</v>
       </c>
       <c r="Y56">
-        <v>0.1514</v>
+        <v>0.0603</v>
       </c>
       <c r="Z56">
-        <v>0.4271</v>
-      </c>
-      <c r="AA56">
-        <v>0.1763</v>
+        <v>0.2367</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>229</v>
       </c>
       <c r="AB56">
-        <v>0.2873</v>
+        <v>0.0206</v>
       </c>
       <c r="AC56" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>225</v>
+        <v>93</v>
       </c>
       <c r="B57">
-        <v>0.1846</v>
-      </c>
-      <c r="C57" t="s">
-        <v>226</v>
+        <v>0.1032</v>
+      </c>
+      <c r="C57">
+        <v>0.2413</v>
       </c>
       <c r="D57">
-        <v>0.0631</v>
-      </c>
-      <c r="E57">
-        <v>0.3392</v>
+        <v>0.22</v>
+      </c>
+      <c r="E57" t="s">
+        <v>231</v>
       </c>
       <c r="F57">
-        <v>0.2832</v>
+        <v>0.1818</v>
       </c>
       <c r="G57" t="s">
-        <v>227</v>
-      </c>
-      <c r="H57">
-        <v>0.2418</v>
+        <v>232</v>
+      </c>
+      <c r="H57" t="s">
+        <v>233</v>
       </c>
       <c r="I57">
-        <v>0.0417</v>
-      </c>
-      <c r="J57">
-        <v>0.2204</v>
+        <v>0.2096</v>
+      </c>
+      <c r="J57" t="s">
+        <v>234</v>
       </c>
       <c r="K57" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="L57">
-        <v>0.0373</v>
+        <v>0.1478</v>
       </c>
       <c r="M57">
-        <v>0.2799</v>
+        <v>0.01</v>
       </c>
       <c r="N57">
-        <v>0.1913</v>
+        <v>0.1699</v>
       </c>
       <c r="O57">
-        <v>0.0526</v>
+        <v>0.0385</v>
       </c>
       <c r="P57">
-        <v>0.2443</v>
+        <v>0.1483</v>
       </c>
       <c r="Q57">
-        <v>0.1743</v>
-      </c>
-      <c r="R57">
-        <v>0.1317</v>
-      </c>
-      <c r="S57">
-        <v>0.1058</v>
+        <v>0.1028</v>
+      </c>
+      <c r="R57" t="s">
+        <v>128</v>
+      </c>
+      <c r="S57" t="s">
+        <v>236</v>
       </c>
       <c r="T57">
-        <v>0.0285</v>
+        <v>0.0924</v>
       </c>
       <c r="U57">
-        <v>0.1501</v>
-      </c>
-      <c r="V57">
-        <v>0.038</v>
-      </c>
-      <c r="W57">
-        <v>0.0967</v>
+        <v>0.0155</v>
+      </c>
+      <c r="V57" t="s">
+        <v>237</v>
+      </c>
+      <c r="W57" t="s">
+        <v>238</v>
       </c>
       <c r="X57">
-        <v>0.0949</v>
+        <v>0.1021</v>
       </c>
       <c r="Y57">
-        <v>0.0603</v>
+        <v>0.2116</v>
       </c>
       <c r="Z57">
-        <v>0.2367</v>
+        <v>0.0959</v>
       </c>
       <c r="AA57" t="s">
-        <v>229</v>
-      </c>
-      <c r="AB57">
-        <v>0.0206</v>
-      </c>
-      <c r="AC57" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>93</v>
-      </c>
-      <c r="B58">
-        <v>0.1032</v>
-      </c>
-      <c r="C58">
-        <v>0.2413</v>
-      </c>
-      <c r="D58">
-        <v>0.22</v>
-      </c>
-      <c r="E58" t="s">
-        <v>231</v>
-      </c>
-      <c r="F58">
-        <v>0.1818</v>
-      </c>
-      <c r="G58" t="s">
-        <v>232</v>
-      </c>
-      <c r="H58" t="s">
-        <v>233</v>
-      </c>
-      <c r="I58">
-        <v>0.2096</v>
-      </c>
-      <c r="J58" t="s">
-        <v>234</v>
-      </c>
-      <c r="K58" t="s">
-        <v>235</v>
-      </c>
-      <c r="L58">
-        <v>0.1478</v>
-      </c>
-      <c r="M58">
-        <v>0.01</v>
-      </c>
-      <c r="N58">
-        <v>0.1699</v>
-      </c>
-      <c r="O58">
-        <v>0.0385</v>
-      </c>
-      <c r="P58">
-        <v>0.1483</v>
-      </c>
-      <c r="Q58">
-        <v>0.1028</v>
-      </c>
-      <c r="R58" t="s">
-        <v>128</v>
-      </c>
-      <c r="S58" t="s">
-        <v>236</v>
-      </c>
-      <c r="T58">
-        <v>0.0924</v>
-      </c>
-      <c r="U58">
-        <v>0.0155</v>
-      </c>
-      <c r="V58" t="s">
-        <v>237</v>
-      </c>
-      <c r="W58" t="s">
-        <v>238</v>
-      </c>
-      <c r="X58">
-        <v>0.1021</v>
-      </c>
-      <c r="Y58">
-        <v>0.2116</v>
-      </c>
-      <c r="Z58">
-        <v>0.0959</v>
-      </c>
-      <c r="AA58" t="s">
         <v>239</v>
       </c>
-      <c r="AB58" t="s">
+      <c r="AB57" t="s">
         <v>240</v>
       </c>
-      <c r="AC58">
+      <c r="AC57">
         <v>0.2625</v>
       </c>
     </row>
